--- a/stella/test_fixtures/pantry_loaded/stars_data.xlsx
+++ b/stella/test_fixtures/pantry_loaded/stars_data.xlsx
@@ -489,19 +489,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>33.9</v>
+        <v>35.6</v>
       </c>
       <c r="E2" t="n">
         <v>12</v>
       </c>
       <c r="F2" t="n">
-        <v>406.76</v>
+        <v>427.18</v>
       </c>
       <c r="G2" t="n">
-        <v>8.16</v>
+        <v>8.43</v>
       </c>
       <c r="H2" t="n">
-        <v>2001.5</v>
+        <v>2030.8</v>
       </c>
     </row>
     <row r="3">
@@ -519,19 +519,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>33.39</v>
+        <v>34.96</v>
       </c>
       <c r="E3" t="n">
         <v>12</v>
       </c>
       <c r="F3" t="n">
-        <v>400.71</v>
+        <v>419.47</v>
       </c>
       <c r="G3" t="n">
-        <v>7.99</v>
+        <v>8.52</v>
       </c>
       <c r="H3" t="n">
-        <v>2000.1</v>
+        <v>2052</v>
       </c>
     </row>
     <row r="4">
@@ -549,19 +549,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>33.92</v>
+        <v>34.15</v>
       </c>
       <c r="E4" t="n">
         <v>12</v>
       </c>
       <c r="F4" t="n">
-        <v>407.02</v>
+        <v>409.85</v>
       </c>
       <c r="G4" t="n">
-        <v>8.16</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="H4" t="n">
-        <v>1999.8</v>
+        <v>2063.3</v>
       </c>
     </row>
     <row r="5">
@@ -579,19 +579,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>35.24</v>
+        <v>34.68</v>
       </c>
       <c r="E5" t="n">
         <v>12</v>
       </c>
       <c r="F5" t="n">
-        <v>422.89</v>
+        <v>416.18</v>
       </c>
       <c r="G5" t="n">
-        <v>8.51</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>2012.1</v>
+        <v>2056.2</v>
       </c>
     </row>
     <row r="6">
@@ -609,19 +609,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>36.52</v>
+        <v>36.26</v>
       </c>
       <c r="E6" t="n">
         <v>12</v>
       </c>
       <c r="F6" t="n">
-        <v>438.18</v>
+        <v>435.1</v>
       </c>
       <c r="G6" t="n">
-        <v>8.859999999999999</v>
+        <v>8.57</v>
       </c>
       <c r="H6" t="n">
-        <v>2036.5</v>
+        <v>2098.3</v>
       </c>
     </row>
     <row r="7">
@@ -639,19 +639,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>36.86</v>
+        <v>35.94</v>
       </c>
       <c r="E7" t="n">
         <v>12</v>
       </c>
       <c r="F7" t="n">
-        <v>442.28</v>
+        <v>431.27</v>
       </c>
       <c r="G7" t="n">
-        <v>8.890000000000001</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="H7" t="n">
-        <v>2068.3</v>
+        <v>2115.2</v>
       </c>
     </row>
     <row r="8">
@@ -669,19 +669,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>37.1</v>
+        <v>37.3</v>
       </c>
       <c r="E8" t="n">
         <v>12</v>
       </c>
       <c r="F8" t="n">
-        <v>445.17</v>
+        <v>447.61</v>
       </c>
       <c r="G8" t="n">
-        <v>8.99</v>
+        <v>8.84</v>
       </c>
       <c r="H8" t="n">
-        <v>2109</v>
+        <v>2147.8</v>
       </c>
     </row>
     <row r="9">
@@ -699,19 +699,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>38.31</v>
+        <v>37.7</v>
       </c>
       <c r="E9" t="n">
         <v>12</v>
       </c>
       <c r="F9" t="n">
-        <v>459.7</v>
+        <v>452.38</v>
       </c>
       <c r="G9" t="n">
-        <v>9.199999999999999</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="H9" t="n">
-        <v>2147.1</v>
+        <v>2181.3</v>
       </c>
     </row>
     <row r="10">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>36.56</v>
+        <v>34.63</v>
       </c>
       <c r="E10" t="n">
         <v>12</v>
       </c>
       <c r="F10" t="n">
-        <v>438.68</v>
+        <v>415.51</v>
       </c>
       <c r="G10" t="n">
-        <v>8.710000000000001</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="H10" t="n">
-        <v>1695.6</v>
+        <v>1734.3</v>
       </c>
     </row>
     <row r="11">
@@ -759,19 +759,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>35.68</v>
+        <v>35.13</v>
       </c>
       <c r="E11" t="n">
         <v>12</v>
       </c>
       <c r="F11" t="n">
-        <v>428.2</v>
+        <v>421.58</v>
       </c>
       <c r="G11" t="n">
         <v>8.43</v>
       </c>
       <c r="H11" t="n">
-        <v>1211.7</v>
+        <v>1274.7</v>
       </c>
     </row>
     <row r="12">
@@ -789,19 +789,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>36.68</v>
+        <v>37</v>
       </c>
       <c r="E12" t="n">
         <v>12</v>
       </c>
       <c r="F12" t="n">
-        <v>440.12</v>
+        <v>444.02</v>
       </c>
       <c r="G12" t="n">
-        <v>8.65</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H12" t="n">
-        <v>793.3</v>
+        <v>818.4</v>
       </c>
     </row>
     <row r="13">
@@ -819,19 +819,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>35.23</v>
+        <v>34.34</v>
       </c>
       <c r="E13" t="n">
         <v>12</v>
       </c>
       <c r="F13" t="n">
-        <v>422.72</v>
+        <v>412.12</v>
       </c>
       <c r="G13" t="n">
-        <v>8.34</v>
+        <v>8.26</v>
       </c>
       <c r="H13" t="n">
-        <v>343.1</v>
+        <v>312.4</v>
       </c>
     </row>
     <row r="14">
@@ -849,16 +849,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>36.39</v>
+        <v>34.57</v>
       </c>
       <c r="E14" t="n">
         <v>12</v>
       </c>
       <c r="F14" t="n">
-        <v>436.72</v>
+        <v>414.89</v>
       </c>
       <c r="G14" t="n">
-        <v>8.56</v>
+        <v>8.18</v>
       </c>
       <c r="H14" t="n">
         <v>200</v>
@@ -879,16 +879,16 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>36.72</v>
+        <v>37.03</v>
       </c>
       <c r="E15" t="n">
         <v>12</v>
       </c>
       <c r="F15" t="n">
-        <v>440.62</v>
+        <v>444.38</v>
       </c>
       <c r="G15" t="n">
-        <v>8.77</v>
+        <v>8.92</v>
       </c>
       <c r="H15" t="n">
         <v>200</v>
@@ -909,16 +909,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>35.99</v>
+        <v>36.57</v>
       </c>
       <c r="E16" t="n">
         <v>12</v>
       </c>
       <c r="F16" t="n">
-        <v>431.86</v>
+        <v>438.83</v>
       </c>
       <c r="G16" t="n">
-        <v>8.51</v>
+        <v>8.77</v>
       </c>
       <c r="H16" t="n">
         <v>200</v>
@@ -939,16 +939,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>37.01</v>
+        <v>34.32</v>
       </c>
       <c r="E17" t="n">
         <v>12</v>
       </c>
       <c r="F17" t="n">
-        <v>444.11</v>
+        <v>411.88</v>
       </c>
       <c r="G17" t="n">
-        <v>9.06</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="H17" t="n">
         <v>200</v>
@@ -969,19 +969,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>25.11</v>
+        <v>26.11</v>
       </c>
       <c r="E18" t="n">
         <v>12</v>
       </c>
       <c r="F18" t="n">
-        <v>301.37</v>
+        <v>313.27</v>
       </c>
       <c r="G18" t="n">
-        <v>6.07</v>
+        <v>6.2</v>
       </c>
       <c r="H18" t="n">
-        <v>217.4</v>
+        <v>227.9</v>
       </c>
     </row>
     <row r="19">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>25.27</v>
+        <v>25.72</v>
       </c>
       <c r="E19" t="n">
         <v>12</v>
       </c>
       <c r="F19" t="n">
-        <v>303.25</v>
+        <v>308.6</v>
       </c>
       <c r="G19" t="n">
-        <v>6.1</v>
+        <v>6.26</v>
       </c>
       <c r="H19" t="n">
-        <v>238.1</v>
+        <v>257.6</v>
       </c>
     </row>
     <row r="20">
@@ -1029,19 +1029,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>24.91</v>
+        <v>25.32</v>
       </c>
       <c r="E20" t="n">
         <v>12</v>
       </c>
       <c r="F20" t="n">
-        <v>298.88</v>
+        <v>303.86</v>
       </c>
       <c r="G20" t="n">
-        <v>5.98</v>
+        <v>6.05</v>
       </c>
       <c r="H20" t="n">
-        <v>269.6</v>
+        <v>281.1</v>
       </c>
     </row>
     <row r="21">
@@ -1059,19 +1059,19 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>24.82</v>
+        <v>25.81</v>
       </c>
       <c r="E21" t="n">
         <v>12</v>
       </c>
       <c r="F21" t="n">
-        <v>297.82</v>
+        <v>309.72</v>
       </c>
       <c r="G21" t="n">
-        <v>6.04</v>
+        <v>6.29</v>
       </c>
       <c r="H21" t="n">
-        <v>296.7</v>
+        <v>314.2</v>
       </c>
     </row>
     <row r="22">
@@ -1089,19 +1089,19 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>25.61</v>
+        <v>24.99</v>
       </c>
       <c r="E22" t="n">
         <v>12</v>
       </c>
       <c r="F22" t="n">
-        <v>307.37</v>
+        <v>299.83</v>
       </c>
       <c r="G22" t="n">
-        <v>6.23</v>
+        <v>5.93</v>
       </c>
       <c r="H22" t="n">
-        <v>315.2</v>
+        <v>337.1</v>
       </c>
     </row>
     <row r="23">
@@ -1119,19 +1119,19 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>24.77</v>
+        <v>26.15</v>
       </c>
       <c r="E23" t="n">
         <v>12</v>
       </c>
       <c r="F23" t="n">
-        <v>297.23</v>
+        <v>313.75</v>
       </c>
       <c r="G23" t="n">
-        <v>5.93</v>
+        <v>6.18</v>
       </c>
       <c r="H23" t="n">
-        <v>323.8</v>
+        <v>367.3</v>
       </c>
     </row>
     <row r="24">
@@ -1149,19 +1149,19 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>31.21</v>
+        <v>32.54</v>
       </c>
       <c r="E24" t="n">
         <v>12</v>
       </c>
       <c r="F24" t="n">
-        <v>374.58</v>
+        <v>390.53</v>
       </c>
       <c r="G24" t="n">
-        <v>7.57</v>
+        <v>7.7</v>
       </c>
       <c r="H24" t="n">
-        <v>421.2</v>
+        <v>487.6</v>
       </c>
     </row>
     <row r="25">
@@ -1179,19 +1179,19 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>32.22</v>
+        <v>31.81</v>
       </c>
       <c r="E25" t="n">
         <v>12</v>
       </c>
       <c r="F25" t="n">
-        <v>386.65</v>
+        <v>381.72</v>
       </c>
       <c r="G25" t="n">
-        <v>7.62</v>
+        <v>7.53</v>
       </c>
       <c r="H25" t="n">
-        <v>529.6</v>
+        <v>582.7</v>
       </c>
     </row>
     <row r="26">
@@ -1209,19 +1209,19 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>33.35</v>
+        <v>31.44</v>
       </c>
       <c r="E26" t="n">
         <v>12</v>
       </c>
       <c r="F26" t="n">
-        <v>400.22</v>
+        <v>377.23</v>
       </c>
       <c r="G26" t="n">
-        <v>7.86</v>
+        <v>7.48</v>
       </c>
       <c r="H26" t="n">
-        <v>610.2</v>
+        <v>621.7</v>
       </c>
     </row>
     <row r="27">
@@ -1239,19 +1239,19 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>31.76</v>
+        <v>31.31</v>
       </c>
       <c r="E27" t="n">
         <v>12</v>
       </c>
       <c r="F27" t="n">
-        <v>381.15</v>
+        <v>375.68</v>
       </c>
       <c r="G27" t="n">
-        <v>7.62</v>
+        <v>7.37</v>
       </c>
       <c r="H27" t="n">
-        <v>670.5</v>
+        <v>678.8</v>
       </c>
     </row>
     <row r="28">
@@ -1269,19 +1269,19 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>32.28</v>
+        <v>31.46</v>
       </c>
       <c r="E28" t="n">
         <v>12</v>
       </c>
       <c r="F28" t="n">
-        <v>387.39</v>
+        <v>377.51</v>
       </c>
       <c r="G28" t="n">
-        <v>7.62</v>
+        <v>7.42</v>
       </c>
       <c r="H28" t="n">
-        <v>728.1</v>
+        <v>740.3</v>
       </c>
     </row>
     <row r="29">
@@ -1299,19 +1299,19 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>33.19</v>
+        <v>32.77</v>
       </c>
       <c r="E29" t="n">
         <v>12</v>
       </c>
       <c r="F29" t="n">
-        <v>398.25</v>
+        <v>393.2</v>
       </c>
       <c r="G29" t="n">
-        <v>8.01</v>
+        <v>7.83</v>
       </c>
       <c r="H29" t="n">
-        <v>804.9</v>
+        <v>803.3</v>
       </c>
     </row>
     <row r="30">
@@ -1329,19 +1329,19 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>32.74</v>
+        <v>32.31</v>
       </c>
       <c r="E30" t="n">
         <v>12</v>
       </c>
       <c r="F30" t="n">
-        <v>392.88</v>
+        <v>387.74</v>
       </c>
       <c r="G30" t="n">
-        <v>7.94</v>
+        <v>7.87</v>
       </c>
       <c r="H30" t="n">
-        <v>825.6</v>
+        <v>828.5</v>
       </c>
     </row>
     <row r="31">
@@ -1359,19 +1359,19 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>31.96</v>
+        <v>31.12</v>
       </c>
       <c r="E31" t="n">
         <v>12</v>
       </c>
       <c r="F31" t="n">
-        <v>383.46</v>
+        <v>373.44</v>
       </c>
       <c r="G31" t="n">
-        <v>7.68</v>
+        <v>7.37</v>
       </c>
       <c r="H31" t="n">
-        <v>854.1</v>
+        <v>824.4</v>
       </c>
     </row>
     <row r="32">
@@ -1389,19 +1389,19 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>33.19</v>
+        <v>31.65</v>
       </c>
       <c r="E32" t="n">
         <v>12</v>
       </c>
       <c r="F32" t="n">
-        <v>398.28</v>
+        <v>379.83</v>
       </c>
       <c r="G32" t="n">
-        <v>7.96</v>
+        <v>7.62</v>
       </c>
       <c r="H32" t="n">
-        <v>889</v>
+        <v>844.2</v>
       </c>
     </row>
     <row r="33">
@@ -1419,19 +1419,19 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>33.21</v>
+        <v>31.14</v>
       </c>
       <c r="E33" t="n">
         <v>12</v>
       </c>
       <c r="F33" t="n">
-        <v>398.52</v>
+        <v>373.62</v>
       </c>
       <c r="G33" t="n">
-        <v>7.97</v>
+        <v>7.43</v>
       </c>
       <c r="H33" t="n">
-        <v>911.8</v>
+        <v>852.8</v>
       </c>
     </row>
   </sheetData>

--- a/stella/test_fixtures/pantry_loaded/stars_data.xlsx
+++ b/stella/test_fixtures/pantry_loaded/stars_data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H33"/>
+  <dimension ref="A1:H49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -485,23 +485,23 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>SF-Original 12ct</t>
+          <t>SF-Whitening 6oz</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>35.6</v>
+        <v>43.99</v>
       </c>
       <c r="E2" t="n">
         <v>12</v>
       </c>
       <c r="F2" t="n">
-        <v>427.18</v>
+        <v>527.9</v>
       </c>
       <c r="G2" t="n">
-        <v>8.43</v>
+        <v>10.49</v>
       </c>
       <c r="H2" t="n">
-        <v>2030.8</v>
+        <v>1013.2</v>
       </c>
     </row>
     <row r="3">
@@ -515,28 +515,28 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>SF-Variety 12ct</t>
+          <t>SF-Sensitivity 4oz</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>34.96</v>
+        <v>41.81</v>
       </c>
       <c r="E3" t="n">
         <v>12</v>
       </c>
       <c r="F3" t="n">
-        <v>419.47</v>
+        <v>501.69</v>
       </c>
       <c r="G3" t="n">
-        <v>8.52</v>
+        <v>9.9</v>
       </c>
       <c r="H3" t="n">
-        <v>2052</v>
+        <v>989.5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>45668</v>
+        <v>45661</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -545,23 +545,23 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>SF-Original 12ct</t>
+          <t>SF-Complete 6oz</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>34.15</v>
+        <v>41</v>
       </c>
       <c r="E4" t="n">
         <v>12</v>
       </c>
       <c r="F4" t="n">
-        <v>409.85</v>
+        <v>491.96</v>
       </c>
       <c r="G4" t="n">
-        <v>8.289999999999999</v>
+        <v>10.02</v>
       </c>
       <c r="H4" t="n">
-        <v>2063.3</v>
+        <v>994.1</v>
       </c>
     </row>
     <row r="5">
@@ -575,28 +575,28 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>SF-Variety 12ct</t>
+          <t>SF-Whitening 6oz</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>34.68</v>
+        <v>43.64</v>
       </c>
       <c r="E5" t="n">
         <v>12</v>
       </c>
       <c r="F5" t="n">
-        <v>416.18</v>
+        <v>523.63</v>
       </c>
       <c r="G5" t="n">
-        <v>8.210000000000001</v>
+        <v>10.55</v>
       </c>
       <c r="H5" t="n">
-        <v>2056.2</v>
+        <v>1030.1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>45675</v>
+        <v>45668</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -605,28 +605,28 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>SF-Original 12ct</t>
+          <t>SF-Sensitivity 4oz</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>36.26</v>
+        <v>41.4</v>
       </c>
       <c r="E6" t="n">
         <v>12</v>
       </c>
       <c r="F6" t="n">
-        <v>435.1</v>
+        <v>496.76</v>
       </c>
       <c r="G6" t="n">
-        <v>8.57</v>
+        <v>10.06</v>
       </c>
       <c r="H6" t="n">
-        <v>2098.3</v>
+        <v>988.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>45675</v>
+        <v>45668</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -635,28 +635,28 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>SF-Variety 12ct</t>
+          <t>SF-Complete 6oz</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>35.94</v>
+        <v>43.91</v>
       </c>
       <c r="E7" t="n">
         <v>12</v>
       </c>
       <c r="F7" t="n">
-        <v>431.27</v>
+        <v>526.86</v>
       </c>
       <c r="G7" t="n">
-        <v>8.630000000000001</v>
+        <v>10.39</v>
       </c>
       <c r="H7" t="n">
-        <v>2115.2</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>45682</v>
+        <v>45675</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -665,28 +665,28 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>SF-Original 12ct</t>
+          <t>SF-Whitening 6oz</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>37.3</v>
+        <v>91.5</v>
       </c>
       <c r="E8" t="n">
         <v>12</v>
       </c>
       <c r="F8" t="n">
-        <v>447.61</v>
+        <v>1097.94</v>
       </c>
       <c r="G8" t="n">
-        <v>8.84</v>
+        <v>21.73</v>
       </c>
       <c r="H8" t="n">
-        <v>2147.8</v>
+        <v>1599.2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>45682</v>
+        <v>45675</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -695,28 +695,28 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>SF-Variety 12ct</t>
+          <t>SF-Sensitivity 4oz</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>37.7</v>
+        <v>92.56999999999999</v>
       </c>
       <c r="E9" t="n">
         <v>12</v>
       </c>
       <c r="F9" t="n">
-        <v>452.38</v>
+        <v>1110.8</v>
       </c>
       <c r="G9" t="n">
-        <v>9.130000000000001</v>
+        <v>22.01</v>
       </c>
       <c r="H9" t="n">
-        <v>2181.3</v>
+        <v>1586.3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>45689</v>
+        <v>45675</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -725,28 +725,28 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>SF-Original 12ct</t>
+          <t>SF-Complete 6oz</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>34.63</v>
+        <v>88.77</v>
       </c>
       <c r="E10" t="n">
         <v>12</v>
       </c>
       <c r="F10" t="n">
-        <v>415.51</v>
+        <v>1065.22</v>
       </c>
       <c r="G10" t="n">
-        <v>8.449999999999999</v>
+        <v>21.09</v>
       </c>
       <c r="H10" t="n">
-        <v>1734.3</v>
+        <v>1567</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>45689</v>
+        <v>45682</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -755,28 +755,28 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>SF-Variety 12ct</t>
+          <t>SF-Whitening 6oz</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>35.13</v>
+        <v>91.19</v>
       </c>
       <c r="E11" t="n">
         <v>12</v>
       </c>
       <c r="F11" t="n">
-        <v>421.58</v>
+        <v>1094.29</v>
       </c>
       <c r="G11" t="n">
-        <v>8.43</v>
+        <v>21.78</v>
       </c>
       <c r="H11" t="n">
-        <v>1274.7</v>
+        <v>2160.7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>45696</v>
+        <v>45682</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -785,28 +785,28 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>SF-Original 12ct</t>
+          <t>SF-Sensitivity 4oz</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>37</v>
+        <v>87.2</v>
       </c>
       <c r="E12" t="n">
         <v>12</v>
       </c>
       <c r="F12" t="n">
-        <v>444.02</v>
+        <v>1046.42</v>
       </c>
       <c r="G12" t="n">
-        <v>8.800000000000001</v>
+        <v>20.51</v>
       </c>
       <c r="H12" t="n">
-        <v>818.4</v>
+        <v>2098.8</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>45696</v>
+        <v>45682</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -815,28 +815,28 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>SF-Variety 12ct</t>
+          <t>SF-Complete 6oz</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>34.34</v>
+        <v>92.78</v>
       </c>
       <c r="E13" t="n">
         <v>12</v>
       </c>
       <c r="F13" t="n">
-        <v>412.12</v>
+        <v>1113.33</v>
       </c>
       <c r="G13" t="n">
-        <v>8.26</v>
+        <v>21.86</v>
       </c>
       <c r="H13" t="n">
-        <v>312.4</v>
+        <v>2155.6</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>45703</v>
+        <v>45689</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -845,28 +845,28 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>SF-Original 12ct</t>
+          <t>SF-Whitening 6oz</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>34.57</v>
+        <v>89.39</v>
       </c>
       <c r="E14" t="n">
         <v>12</v>
       </c>
       <c r="F14" t="n">
-        <v>414.89</v>
+        <v>1072.62</v>
       </c>
       <c r="G14" t="n">
-        <v>8.18</v>
+        <v>21.72</v>
       </c>
       <c r="H14" t="n">
-        <v>200</v>
+        <v>2137.3</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>45703</v>
+        <v>45689</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -875,28 +875,28 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>SF-Variety 12ct</t>
+          <t>SF-Sensitivity 4oz</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>37.03</v>
+        <v>88.5</v>
       </c>
       <c r="E15" t="n">
         <v>12</v>
       </c>
       <c r="F15" t="n">
-        <v>444.38</v>
+        <v>1062.02</v>
       </c>
       <c r="G15" t="n">
-        <v>8.92</v>
+        <v>21.45</v>
       </c>
       <c r="H15" t="n">
-        <v>200</v>
+        <v>2075.5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>45710</v>
+        <v>45689</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -905,28 +905,28 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>SF-Original 12ct</t>
+          <t>SF-Complete 6oz</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>36.57</v>
+        <v>87.03</v>
       </c>
       <c r="E16" t="n">
         <v>12</v>
       </c>
       <c r="F16" t="n">
-        <v>438.83</v>
+        <v>1044.34</v>
       </c>
       <c r="G16" t="n">
-        <v>8.77</v>
+        <v>20.63</v>
       </c>
       <c r="H16" t="n">
-        <v>200</v>
+        <v>2090.6</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>45710</v>
+        <v>45696</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -935,28 +935,28 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>SF-Variety 12ct</t>
+          <t>SF-Whitening 6oz</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>34.32</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="E17" t="n">
         <v>12</v>
       </c>
       <c r="F17" t="n">
-        <v>411.88</v>
+        <v>1069.24</v>
       </c>
       <c r="G17" t="n">
-        <v>8.109999999999999</v>
+        <v>21.69</v>
       </c>
       <c r="H17" t="n">
-        <v>200</v>
+        <v>2092.8</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>45717</v>
+        <v>45696</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -965,28 +965,28 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>SF-Original 12ct</t>
+          <t>SF-Sensitivity 4oz</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>26.11</v>
+        <v>90.61</v>
       </c>
       <c r="E18" t="n">
         <v>12</v>
       </c>
       <c r="F18" t="n">
-        <v>313.27</v>
+        <v>1087.31</v>
       </c>
       <c r="G18" t="n">
-        <v>6.2</v>
+        <v>22.17</v>
       </c>
       <c r="H18" t="n">
-        <v>227.9</v>
+        <v>2028.1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>45717</v>
+        <v>45696</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -995,28 +995,28 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>SF-Variety 12ct</t>
+          <t>SF-Complete 6oz</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>25.72</v>
+        <v>88.56</v>
       </c>
       <c r="E19" t="n">
         <v>12</v>
       </c>
       <c r="F19" t="n">
-        <v>308.6</v>
+        <v>1062.72</v>
       </c>
       <c r="G19" t="n">
-        <v>6.26</v>
+        <v>21.61</v>
       </c>
       <c r="H19" t="n">
-        <v>257.6</v>
+        <v>2039.5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>45724</v>
+        <v>45703</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -1025,28 +1025,28 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>SF-Original 12ct</t>
+          <t>SF-Whitening 6oz</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>25.32</v>
+        <v>90.89</v>
       </c>
       <c r="E20" t="n">
         <v>12</v>
       </c>
       <c r="F20" t="n">
-        <v>303.86</v>
+        <v>1090.69</v>
       </c>
       <c r="G20" t="n">
-        <v>6.05</v>
+        <v>22.04</v>
       </c>
       <c r="H20" t="n">
-        <v>281.1</v>
+        <v>2083.8</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>45724</v>
+        <v>45703</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -1055,28 +1055,28 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>SF-Variety 12ct</t>
+          <t>SF-Sensitivity 4oz</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>25.81</v>
+        <v>89.02</v>
       </c>
       <c r="E21" t="n">
         <v>12</v>
       </c>
       <c r="F21" t="n">
-        <v>309.72</v>
+        <v>1068.28</v>
       </c>
       <c r="G21" t="n">
-        <v>6.29</v>
+        <v>21.11</v>
       </c>
       <c r="H21" t="n">
-        <v>314.2</v>
+        <v>2010.7</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>45731</v>
+        <v>45703</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -1085,28 +1085,28 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>SF-Original 12ct</t>
+          <t>SF-Complete 6oz</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>24.99</v>
+        <v>88.98999999999999</v>
       </c>
       <c r="E22" t="n">
         <v>12</v>
       </c>
       <c r="F22" t="n">
-        <v>299.83</v>
+        <v>1067.9</v>
       </c>
       <c r="G22" t="n">
-        <v>5.93</v>
+        <v>21.18</v>
       </c>
       <c r="H22" t="n">
-        <v>337.1</v>
+        <v>2013.9</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>45731</v>
+        <v>45710</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -1115,28 +1115,28 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>SF-Variety 12ct</t>
+          <t>SF-Whitening 6oz</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>26.15</v>
+        <v>92.16</v>
       </c>
       <c r="E23" t="n">
         <v>12</v>
       </c>
       <c r="F23" t="n">
-        <v>313.75</v>
+        <v>1105.92</v>
       </c>
       <c r="G23" t="n">
-        <v>6.18</v>
+        <v>22.39</v>
       </c>
       <c r="H23" t="n">
-        <v>367.3</v>
+        <v>2041.3</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>45738</v>
+        <v>45710</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -1145,28 +1145,28 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>SF-Original 12ct</t>
+          <t>SF-Sensitivity 4oz</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>32.54</v>
+        <v>87.64</v>
       </c>
       <c r="E24" t="n">
         <v>12</v>
       </c>
       <c r="F24" t="n">
-        <v>390.53</v>
+        <v>1051.65</v>
       </c>
       <c r="G24" t="n">
-        <v>7.7</v>
+        <v>20.83</v>
       </c>
       <c r="H24" t="n">
-        <v>487.6</v>
+        <v>1962.1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>45738</v>
+        <v>45710</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -1175,28 +1175,28 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>SF-Variety 12ct</t>
+          <t>SF-Complete 6oz</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>31.81</v>
+        <v>92.42</v>
       </c>
       <c r="E25" t="n">
         <v>12</v>
       </c>
       <c r="F25" t="n">
-        <v>381.72</v>
+        <v>1109.02</v>
       </c>
       <c r="G25" t="n">
-        <v>7.53</v>
+        <v>22.09</v>
       </c>
       <c r="H25" t="n">
-        <v>582.7</v>
+        <v>2032.9</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>45745</v>
+        <v>45717</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -1205,28 +1205,28 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>SF-Original 12ct</t>
+          <t>SF-Whitening 6oz</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>31.44</v>
+        <v>30.58</v>
       </c>
       <c r="E26" t="n">
         <v>12</v>
       </c>
       <c r="F26" t="n">
-        <v>377.23</v>
+        <v>366.9</v>
       </c>
       <c r="G26" t="n">
-        <v>7.48</v>
+        <v>7.31</v>
       </c>
       <c r="H26" t="n">
-        <v>621.7</v>
+        <v>2024.3</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>45745</v>
+        <v>45717</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -1235,28 +1235,28 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>SF-Variety 12ct</t>
+          <t>SF-Sensitivity 4oz</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>31.31</v>
+        <v>28.95</v>
       </c>
       <c r="E27" t="n">
         <v>12</v>
       </c>
       <c r="F27" t="n">
-        <v>375.68</v>
+        <v>347.35</v>
       </c>
       <c r="G27" t="n">
-        <v>7.37</v>
+        <v>6.99</v>
       </c>
       <c r="H27" t="n">
-        <v>678.8</v>
+        <v>1931.8</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>45752</v>
+        <v>45717</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -1265,28 +1265,28 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>SF-Original 12ct</t>
+          <t>SF-Complete 6oz</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>31.46</v>
+        <v>29.06</v>
       </c>
       <c r="E28" t="n">
         <v>12</v>
       </c>
       <c r="F28" t="n">
-        <v>377.51</v>
+        <v>348.74</v>
       </c>
       <c r="G28" t="n">
-        <v>7.42</v>
+        <v>7.09</v>
       </c>
       <c r="H28" t="n">
-        <v>740.3</v>
+        <v>1980.9</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>45752</v>
+        <v>45724</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -1295,28 +1295,28 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>SF-Variety 12ct</t>
+          <t>SF-Whitening 6oz</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>32.77</v>
+        <v>30.58</v>
       </c>
       <c r="E29" t="n">
         <v>12</v>
       </c>
       <c r="F29" t="n">
-        <v>393.2</v>
+        <v>366.95</v>
       </c>
       <c r="G29" t="n">
-        <v>7.83</v>
+        <v>7.26</v>
       </c>
       <c r="H29" t="n">
-        <v>803.3</v>
+        <v>1972.8</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>45759</v>
+        <v>45724</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -1325,28 +1325,28 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>SF-Original 12ct</t>
+          <t>SF-Sensitivity 4oz</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>32.31</v>
+        <v>30.62</v>
       </c>
       <c r="E30" t="n">
         <v>12</v>
       </c>
       <c r="F30" t="n">
-        <v>387.74</v>
+        <v>367.49</v>
       </c>
       <c r="G30" t="n">
-        <v>7.87</v>
+        <v>7.29</v>
       </c>
       <c r="H30" t="n">
-        <v>828.5</v>
+        <v>1906.4</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>45759</v>
+        <v>45724</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -1355,28 +1355,28 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>SF-Variety 12ct</t>
+          <t>SF-Complete 6oz</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>31.12</v>
+        <v>30.37</v>
       </c>
       <c r="E31" t="n">
         <v>12</v>
       </c>
       <c r="F31" t="n">
-        <v>373.44</v>
+        <v>364.42</v>
       </c>
       <c r="G31" t="n">
-        <v>7.37</v>
+        <v>7.18</v>
       </c>
       <c r="H31" t="n">
-        <v>824.4</v>
+        <v>1934.3</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>45766</v>
+        <v>45731</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -1385,53 +1385,533 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>SF-Original 12ct</t>
+          <t>SF-Whitening 6oz</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>31.65</v>
+        <v>35.19</v>
       </c>
       <c r="E32" t="n">
         <v>12</v>
       </c>
       <c r="F32" t="n">
-        <v>379.83</v>
+        <v>422.31</v>
       </c>
       <c r="G32" t="n">
-        <v>7.62</v>
+        <v>8.52</v>
       </c>
       <c r="H32" t="n">
-        <v>844.2</v>
+        <v>1957.2</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
+        <v>45731</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>SF-Sensitivity 4oz</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>35.02</v>
+      </c>
+      <c r="E33" t="n">
+        <v>12</v>
+      </c>
+      <c r="F33" t="n">
+        <v>420.29</v>
+      </c>
+      <c r="G33" t="n">
+        <v>8.42</v>
+      </c>
+      <c r="H33" t="n">
+        <v>1900.2</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>45731</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>SF-Complete 6oz</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>34.87</v>
+      </c>
+      <c r="E34" t="n">
+        <v>12</v>
+      </c>
+      <c r="F34" t="n">
+        <v>418.46</v>
+      </c>
+      <c r="G34" t="n">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="H34" t="n">
+        <v>1916.1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="n">
+        <v>45738</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>SF-Whitening 6oz</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>32.96</v>
+      </c>
+      <c r="E35" t="n">
+        <v>12</v>
+      </c>
+      <c r="F35" t="n">
+        <v>395.53</v>
+      </c>
+      <c r="G35" t="n">
+        <v>7.83</v>
+      </c>
+      <c r="H35" t="n">
+        <v>1917.2</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>45738</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>SF-Sensitivity 4oz</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>34.01</v>
+      </c>
+      <c r="E36" t="n">
+        <v>12</v>
+      </c>
+      <c r="F36" t="n">
+        <v>408.17</v>
+      </c>
+      <c r="G36" t="n">
+        <v>8.19</v>
+      </c>
+      <c r="H36" t="n">
+        <v>1865.1</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n">
+        <v>45738</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>SF-Complete 6oz</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>34.78</v>
+      </c>
+      <c r="E37" t="n">
+        <v>12</v>
+      </c>
+      <c r="F37" t="n">
+        <v>417.36</v>
+      </c>
+      <c r="G37" t="n">
+        <v>8.49</v>
+      </c>
+      <c r="H37" t="n">
+        <v>1893.6</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n">
+        <v>45745</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>SF-Whitening 6oz</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>41.14</v>
+      </c>
+      <c r="E38" t="n">
+        <v>12</v>
+      </c>
+      <c r="F38" t="n">
+        <v>493.67</v>
+      </c>
+      <c r="G38" t="n">
+        <v>9.94</v>
+      </c>
+      <c r="H38" t="n">
+        <v>1960.1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="n">
+        <v>45745</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>SF-Sensitivity 4oz</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>39.37</v>
+      </c>
+      <c r="E39" t="n">
+        <v>12</v>
+      </c>
+      <c r="F39" t="n">
+        <v>472.43</v>
+      </c>
+      <c r="G39" t="n">
+        <v>9.56</v>
+      </c>
+      <c r="H39" t="n">
+        <v>1877.1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="n">
+        <v>45745</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>SF-Complete 6oz</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>41.09</v>
+      </c>
+      <c r="E40" t="n">
+        <v>12</v>
+      </c>
+      <c r="F40" t="n">
+        <v>493.1</v>
+      </c>
+      <c r="G40" t="n">
+        <v>10.03</v>
+      </c>
+      <c r="H40" t="n">
+        <v>1910.1</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="n">
+        <v>45752</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>SF-Whitening 6oz</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>39.9</v>
+      </c>
+      <c r="E41" t="n">
+        <v>12</v>
+      </c>
+      <c r="F41" t="n">
+        <v>478.77</v>
+      </c>
+      <c r="G41" t="n">
+        <v>9.630000000000001</v>
+      </c>
+      <c r="H41" t="n">
+        <v>1946.2</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n">
+        <v>45752</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>SF-Sensitivity 4oz</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>41.95</v>
+      </c>
+      <c r="E42" t="n">
+        <v>12</v>
+      </c>
+      <c r="F42" t="n">
+        <v>503.36</v>
+      </c>
+      <c r="G42" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="H42" t="n">
+        <v>1906.6</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="n">
+        <v>45752</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>SF-Complete 6oz</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>41.59</v>
+      </c>
+      <c r="E43" t="n">
+        <v>12</v>
+      </c>
+      <c r="F43" t="n">
+        <v>499.06</v>
+      </c>
+      <c r="G43" t="n">
+        <v>9.890000000000001</v>
+      </c>
+      <c r="H43" t="n">
+        <v>1937.5</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="n">
+        <v>45759</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>SF-Whitening 6oz</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>40</v>
+      </c>
+      <c r="E44" t="n">
+        <v>12</v>
+      </c>
+      <c r="F44" t="n">
+        <v>479.96</v>
+      </c>
+      <c r="G44" t="n">
+        <v>9.779999999999999</v>
+      </c>
+      <c r="H44" t="n">
+        <v>1925.3</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="n">
+        <v>45759</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>SF-Sensitivity 4oz</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>39.73</v>
+      </c>
+      <c r="E45" t="n">
+        <v>12</v>
+      </c>
+      <c r="F45" t="n">
+        <v>476.8</v>
+      </c>
+      <c r="G45" t="n">
+        <v>9.640000000000001</v>
+      </c>
+      <c r="H45" t="n">
+        <v>1879</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="n">
+        <v>45759</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>SF-Complete 6oz</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>40.72</v>
+      </c>
+      <c r="E46" t="n">
+        <v>12</v>
+      </c>
+      <c r="F46" t="n">
+        <v>488.62</v>
+      </c>
+      <c r="G46" t="n">
+        <v>9.83</v>
+      </c>
+      <c r="H46" t="n">
+        <v>1942.6</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="n">
         <v>45766</v>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Summit Foods</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>SF-Variety 12ct</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>31.14</v>
-      </c>
-      <c r="E33" t="n">
-        <v>12</v>
-      </c>
-      <c r="F33" t="n">
-        <v>373.62</v>
-      </c>
-      <c r="G33" t="n">
-        <v>7.43</v>
-      </c>
-      <c r="H33" t="n">
-        <v>852.8</v>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>SF-Whitening 6oz</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>38.84</v>
+      </c>
+      <c r="E47" t="n">
+        <v>12</v>
+      </c>
+      <c r="F47" t="n">
+        <v>466.07</v>
+      </c>
+      <c r="G47" t="n">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="H47" t="n">
+        <v>1869</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="n">
+        <v>45766</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>SF-Sensitivity 4oz</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>40.58</v>
+      </c>
+      <c r="E48" t="n">
+        <v>12</v>
+      </c>
+      <c r="F48" t="n">
+        <v>486.96</v>
+      </c>
+      <c r="G48" t="n">
+        <v>9.74</v>
+      </c>
+      <c r="H48" t="n">
+        <v>1847.8</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="n">
+        <v>45766</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>SF-Complete 6oz</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>39.88</v>
+      </c>
+      <c r="E49" t="n">
+        <v>12</v>
+      </c>
+      <c r="F49" t="n">
+        <v>478.62</v>
+      </c>
+      <c r="G49" t="n">
+        <v>9.710000000000001</v>
+      </c>
+      <c r="H49" t="n">
+        <v>1929.3</v>
       </c>
     </row>
   </sheetData>
